--- a/AAII_Financials/Quarterly/BCH_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BCH_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="92">
   <si>
     <t>BCH</t>
   </si>
@@ -656,343 +656,350 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>821600</v>
+      </c>
+      <c r="E8" s="3">
         <v>682600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>702400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>682300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>715300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>723900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>679100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>713700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>717100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>681000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>838500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>695400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>847800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>753600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1222900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1340600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1312600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>944400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1015000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>679600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>615600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>546000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>574300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>418300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>546600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>659600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>724200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>693200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>829400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>559900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>667200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>630400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>634800</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>601400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>705400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>579000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>809800</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>671400</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>702900</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>721300</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3">
+      <c r="D9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E9" s="3">
         <v>14300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>15700</v>
       </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I9" s="3">
         <v>13000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12800</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L9" s="3">
+      <c r="L9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M9" s="3">
         <v>14000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>15800</v>
       </c>
-      <c r="N9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P9" s="3">
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="3">
         <v>12800</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1068,53 +1075,56 @@
       <c r="AP9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>821600</v>
+      </c>
+      <c r="E10" s="3">
         <v>668400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>686700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>682300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>715300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>710900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>666300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>713700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>717100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>667000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>822700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>695400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>847800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>740800</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1190,8 +1200,11 @@
       <c r="AP10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1234,8 +1247,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1356,8 +1370,11 @@
       <c r="AP12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1478,47 +1495,50 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>200</v>
+      </c>
+      <c r="E14" s="3">
         <v>300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1200</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>1500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>100</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
@@ -1600,121 +1620,124 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E15" s="3">
         <v>17900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>6600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>6000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>6600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>17100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>6800</v>
-      </c>
-      <c r="J15" s="3">
-        <v>7800</v>
       </c>
       <c r="K15" s="3">
         <v>7800</v>
       </c>
       <c r="L15" s="3">
+        <v>7800</v>
+      </c>
+      <c r="M15" s="3">
         <v>16500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>8900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>8700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>18000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>-23100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>-23800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>-22400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>-22500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>-23200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>-24200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>-24100</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>-20900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>-20500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>-21800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>-21900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>-22000</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>-23700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>-23400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>-24100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>-22400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>-12400</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>-11700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>-11900</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>-11700</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>-13300</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>-13200</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>-12700</v>
-      </c>
-      <c r="AN15" s="3">
-        <v>-12600</v>
       </c>
       <c r="AO15" s="3">
         <v>-12600</v>
@@ -1722,8 +1745,11 @@
       <c r="AP15" s="3">
         <v>-12600</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>-12600</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1763,252 +1789,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>313200</v>
+      </c>
+      <c r="E17" s="3">
         <v>309300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>324300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>287000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>299000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>295000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>303900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>304200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>287900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>289800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>361800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>301500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>329400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>332600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>780900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>768600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>703100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>420100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>576800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>330200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>284300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>231800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>280000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>181600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>317400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>392900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>389200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>355500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>417900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>284500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>314000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>335700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>280000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>287100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>323900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>236400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>425600</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>318000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>372400</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>352500</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>508400</v>
+      </c>
+      <c r="E18" s="3">
         <v>373300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>378200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>395300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>416300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>428900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>375200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>409500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>429200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>391200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>476800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>393900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>518400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>421100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>442100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>572000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>609600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>524300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>438200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>349400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>331200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>314200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>294300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>236600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>229100</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>266700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>335000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>337700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>411500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>275400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>353200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>294600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>354800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>314300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>381500</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>342700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>384200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>353400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>330400</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>368900</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2051,8 +2084,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2095,208 +2129,214 @@
       <c r="P20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R20" s="3">
         <v>6900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-121500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-74500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-127200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-49300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-56000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-75600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-86600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-118700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-98600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-52100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-65500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-90600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-75300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-78200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-98900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-67600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-95300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-105400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-95600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-125500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-110000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-104600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-105900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-114200</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>-116200</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>514600</v>
+      </c>
+      <c r="E21" s="3">
         <v>391200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>384700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>401400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>422900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>446100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>382000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>417300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>437100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>407700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>485600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>402600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>519600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>439000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>472000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>474300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>557400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>419600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>412100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>317700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>279800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>248500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>196100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>159800</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>198900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>223200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>268100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>285800</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>357400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>198800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>298000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>211000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>261300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>230500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>269300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>245900</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>292300</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>260100</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>228900</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>265300</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2339,8 +2379,8 @@
       <c r="P22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
+      <c r="Q22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R22" s="3">
         <v>0</v>
@@ -2417,252 +2457,261 @@
       <c r="AP22" s="3">
         <v>0</v>
       </c>
+      <c r="AQ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>508300</v>
+      </c>
+      <c r="E23" s="3">
         <v>373000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>377600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>394900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>413700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>428600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>374100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>409600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>427700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>391300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>474800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>393800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>518400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>421100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>448900</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>450600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>535100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>397100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>388900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>293500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>255700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>227600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>175500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>138100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>177000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>201300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>244500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>262400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>333300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>176400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>285600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>199300</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>249400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>218700</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>256000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>232700</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>279600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>247600</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>216200</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>252700</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>84300</v>
+      </c>
+      <c r="E24" s="3">
         <v>84100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>82800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>90300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>86400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>83000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>74100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>88600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>84400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>87400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>35000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>102700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>104500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>85300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>74600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>80400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>77600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>67400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>56800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>61300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>51100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>45600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>35400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>35700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>38500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>38400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>57600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>55400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>68200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>44400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>80500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>40400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>41300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>36100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>46700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>35900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>44700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>41800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>28900</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>34200</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2783,252 +2832,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>423900</v>
+      </c>
+      <c r="E26" s="3">
         <v>288900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>294800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>304600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>327300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>345600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>299900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>321000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>343300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>303800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>439800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>291100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>413800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>335700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>374300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>370100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>457400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>329700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>332100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>232100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>204600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>182000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>140200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>102400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>138500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>162900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>186900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>207000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>265100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>132000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>205100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>158900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>208100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>182600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>209300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>196800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>234900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>205800</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>187300</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>218500</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>423900</v>
+      </c>
+      <c r="E27" s="3">
         <v>288900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>294800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>304600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>327300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>345600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>299900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>321000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>343300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>303800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>439800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>291100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>413800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>335700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>374300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>370100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>457400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>329700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>332100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>232100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>204600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>182000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>140200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>102400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>138500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>162900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>186900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>207000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>265100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>132000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>205100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>158900</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>208100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>182600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>209300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>196800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>234900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>205800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>187300</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>218500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3149,8 +3207,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3271,8 +3332,11 @@
       <c r="AP29" s="3">
         <v>0</v>
       </c>
+      <c r="AQ29" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3393,8 +3457,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3515,8 +3582,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3559,208 +3629,214 @@
       <c r="P32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R32" s="3">
         <v>-6900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>121500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>74500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>127200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>49300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>56000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>75600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>86600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>118700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>98600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>52100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>65500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>90600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>75300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>78200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>98900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>67600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>95300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>105400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>95600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>125500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>110000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>104600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>105900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>114200</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>116200</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>423900</v>
+      </c>
+      <c r="E33" s="3">
         <v>288900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>294800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>304600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>327300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>345600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>299900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>321000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>343300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>303800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>439800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>291100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>413800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>335700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>374300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>370100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>457400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>329700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>332100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>232100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>204600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>182000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>140200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>102400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>138500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>162900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>186900</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>207000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>265100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>132000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>205100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>158900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>208100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>182600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>209300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>196800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>234900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>205800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>187300</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>218500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3881,257 +3957,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>423900</v>
+      </c>
+      <c r="E35" s="3">
         <v>288900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>294800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>304600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>327300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>345600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>299900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>321000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>343300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>303800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>439800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>291100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>413800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>335700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>374300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>370100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>457400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>329700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>332100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>232100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>204600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>182000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>140200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>102400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>138500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>162900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>186900</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>207000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>265100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>132000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>205100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>158900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>208100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>182600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>209300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>196800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>234900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>205800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>187300</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>218500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4174,8 +4259,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4218,297 +4304,304 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1837200</v>
+      </c>
+      <c r="E41" s="3">
         <v>2454000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1840500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2386500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2469400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2492800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2047900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2600800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2454700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2519900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2611700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3233200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2866100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3745000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4620500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5543200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4991400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8010600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5528100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4933500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6673400</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7094900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5304700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4583300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4216200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4060100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3546400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3694500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>4361500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3350700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3583100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3428900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3538600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>2836400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2891200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>3077300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>2958500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>3387100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>3523000</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>3447400</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>5746300</v>
+      </c>
+      <c r="E42" s="3">
         <v>5897900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6132300</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>5764900</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>5595700</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>5541000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>4619700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>5776000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>5282700</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>5779700</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8879300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>9268600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>10289900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>8588900</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>5621600</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>4112600</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>4714800</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>2058900</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>9382300</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>9670400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>8244600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>5799000</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>9616000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>9453500</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>11532500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>9205000</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>7778400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>6750600</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>4533900</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>4327400</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>4432300</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>4120600</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>3732800</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>4057800</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>4892500</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>3759300</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>4831100</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>4779700</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>4568200</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>4469300</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>961600</v>
+      </c>
+      <c r="E43" s="3">
         <v>1058500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1129400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>992400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1056300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1051000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>927800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1402700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1101900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>887000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>841600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>824000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>795700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>888400</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
@@ -4584,53 +4677,56 @@
       <c r="AP43" s="3">
         <v>0</v>
       </c>
+      <c r="AQ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>32700</v>
+      </c>
+      <c r="E44" s="3">
         <v>27800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>28400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>30500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>34600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>34800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>33700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>33000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>26500</v>
-      </c>
-      <c r="L44" s="3">
-        <v>26100</v>
       </c>
       <c r="M44" s="3">
         <v>26100</v>
       </c>
       <c r="N44" s="3">
+        <v>26100</v>
+      </c>
+      <c r="O44" s="3">
         <v>21200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>19700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>14600</v>
       </c>
-      <c r="Q44" s="3">
-        <v>0</v>
-      </c>
       <c r="R44" s="3">
         <v>0</v>
       </c>
@@ -4706,8 +4802,11 @@
       <c r="AP44" s="3">
         <v>0</v>
       </c>
+      <c r="AQ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4738,20 +4837,20 @@
       <c r="L45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N45" s="3">
         <v>280200</v>
       </c>
-      <c r="N45" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
       <c r="P45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q45" s="3">
-        <v>0</v>
+      <c r="Q45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R45" s="3">
         <v>0</v>
@@ -4828,53 +4927,56 @@
       <c r="AP45" s="3">
         <v>0</v>
       </c>
+      <c r="AQ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>9307400</v>
+      </c>
+      <c r="E46" s="3">
         <v>10269900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>11197800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>10020800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>10568000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9933100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9090900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>10625000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>10221700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>10824400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>13764100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>14555300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>14934800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>14246700</v>
       </c>
-      <c r="Q46" s="3">
-        <v>0</v>
-      </c>
       <c r="R46" s="3">
         <v>0</v>
       </c>
@@ -4950,374 +5052,386 @@
       <c r="AP46" s="3">
         <v>0</v>
       </c>
+      <c r="AQ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>5503400</v>
+      </c>
+      <c r="E47" s="3">
         <v>4480200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4548300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>3978100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3761300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3105700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3128800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>3303600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3960700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3967600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>6039200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5047000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>6534900</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7624700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>67200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>65100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>60500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>61400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>57500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>60600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>54900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>49300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>49600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>56800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>63600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>62600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>64500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>66900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>65800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>59400</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>56600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>55000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>53200</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>49900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>55900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>53600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>51200</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>50200</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>49200</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>48000</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>280000</v>
+      </c>
+      <c r="E48" s="3">
         <v>271100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>287200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>274300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>291200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>293100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>287800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>328000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>312000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>307900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>354200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>330000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>373500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>387000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>342500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>352100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>348500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>368600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>391900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>427700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>436100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>395700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>388000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>417600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>459900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>456900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>487800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>526400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>536200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>506100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>291900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>285700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>290400</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>289800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>338900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>338500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>338100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>340900</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>353000</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>350300</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>194400</v>
+      </c>
+      <c r="E49" s="3">
         <v>189300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>193800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>174800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>176900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>170600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>159600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>170800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>159200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>147200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>156500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>142800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>147900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>139100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>115100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>94700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>84500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>82100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>84900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>86200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>84200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>70000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>67400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>69700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>73700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>69900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>74000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>74500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>75100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>68900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>66100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>60000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>58300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>53500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>57400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>49900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>45000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>44100</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>44300</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>42500</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5438,8 +5552,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5560,130 +5677,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>149700</v>
+      </c>
+      <c r="E52" s="3">
         <v>159800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>184300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>172000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>195400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>175900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>196400</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>214400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1490900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3690700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>220500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>240700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>180700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>173500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>594400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>582600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>535200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>525100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>513900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>488000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>481100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>396100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>397300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>386700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>402000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>376800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>407600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>429800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>441500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>359500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>353000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>331800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>333300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>339900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>393100</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>436900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>435600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>433600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>425400</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>433000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5804,130 +5927,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>59955200</v>
+      </c>
+      <c r="E54" s="3">
         <v>59576800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>60060700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>57684600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>57250000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>56494000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>52424700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>57597300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>56822900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>57964700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>63638500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>61757700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>67621700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>69364900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>59675800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>59746700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>57562600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>56484100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>60491900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>62015200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>59618500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>50383600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>51165600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>52582700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>57216900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>53308100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>52417100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>53648400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>51411400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>46920100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>45626600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>43505300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>43981900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>42552000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>48251600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>46956400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>47447700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>46794000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>47615900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>46838400</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5970,8 +6099,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6014,419 +6144,429 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>32856100</v>
+      </c>
+      <c r="E57" s="3">
         <v>32990400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>32090200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>31175600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>31849600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>32116900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29040100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>31658900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>31131100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>30205800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>33111900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>31713800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>35191400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>35593700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1293300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>946100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1105900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1114700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>796700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>720900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1258300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1192300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>1748400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>1419500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>981800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>835500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>741200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>892200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>1324600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>1014300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>650700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>855600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>770600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>834400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>714200</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>723800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>1213600</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>773100</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>515500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>680800</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6207600</v>
+      </c>
+      <c r="E58" s="3">
         <v>4375900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5302200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>4545900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4596500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4485100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3840400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3986300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6751100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9828600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>9285300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>10644800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>10268300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>11685800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>3474200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3129000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>2827100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>2043400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>3923700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>4422900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>4534600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>4097700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>2679200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>2580000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>3428900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>3912700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>3974500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>4593000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>4598600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>3662400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>3931500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>3540700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>3309200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3137700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3693500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>3661200</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>3726400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>3443200</v>
       </c>
-      <c r="AO58" s="3">
-        <v>0</v>
-      </c>
       <c r="AP58" s="3">
         <v>0</v>
       </c>
+      <c r="AQ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1599400</v>
+      </c>
+      <c r="E59" s="3">
         <v>1510900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1975000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1696900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1331900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1362500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1365000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1661700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1223600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>998400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1706300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1556000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1327500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1561200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>576500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>425700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>308700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>279700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>517300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>396400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>218000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>84900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>249600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>203300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>154200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>153700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>480300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>385800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>309200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>120800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>415800</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>277700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>202400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>99500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>466800</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>352500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>235000</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>110600</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>432900</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>339800</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>40669900</v>
+      </c>
+      <c r="E60" s="3">
         <v>38887300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>39518500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>37422800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>37905400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>37975400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>34393900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>37445700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>39229000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>41139700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>44278900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>44048800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>46923800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>48960500</v>
       </c>
-      <c r="Q60" s="3">
-        <v>0</v>
-      </c>
       <c r="R60" s="3">
         <v>0</v>
       </c>
@@ -6502,252 +6642,261 @@
       <c r="AP60" s="3">
         <v>0</v>
       </c>
+      <c r="AQ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>11359700</v>
+      </c>
+      <c r="E61" s="3">
         <v>13173300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>12695500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>12716900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>12033000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>11688200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>11265900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>12623900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>10266500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>10020100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>12067600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>10812400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>12864300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13015900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>14158100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13959000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13699100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>14252300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>13399400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>13270600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>13378800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>10593500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>11594300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>12603900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>13852000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>9816300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>9979800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>10302500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>9268000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>8462600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>8024500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>7630200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>7685300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>7531900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>8090800</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>7957500</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>8136900</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>8411800</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>11180300</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>11255500</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1517800</v>
+      </c>
+      <c r="E62" s="3">
         <v>1450000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1313500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1597300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1242900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1119700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1016900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1335800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1574600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1428900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1215800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1160900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1646400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1327900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1017100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>995000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>904700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>884600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>847200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>826600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>740200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>587600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>570100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>488400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>554900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>429400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>487900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>502900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>494600</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>440400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>463200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>439600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>454100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>458700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>563000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>590800</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>576700</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>553100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>569000</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>589100</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6868,8 +7017,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6990,8 +7142,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7112,130 +7267,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>53749300</v>
+      </c>
+      <c r="E66" s="3">
         <v>53701500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>53622300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>51776200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>51272300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>50825300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>46766100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>51496800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>51159500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>52682900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>57664800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>56129700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>61551600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>63428100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>54428800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>54639300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>52870500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>51738200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>55550900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>56922800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>54662200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>46105100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>47029400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>48370200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>52779000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>49082500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>47936300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>48991800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>46729600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>42628800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>41430300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>39508100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>39927200</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>38580100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>43686200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>42491400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>43061400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>42536500</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>43255900</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>42530100</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7278,8 +7439,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7400,8 +7562,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7522,8 +7687,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7644,8 +7812,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7766,130 +7937,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2845600</v>
+      </c>
+      <c r="E72" s="3">
         <v>2567800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2972000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2651000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2594400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2381000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2504700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2593600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2318100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2061500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2375700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2101000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2197900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2003400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2741100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2520700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2211900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2013800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2107900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2030400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1953600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1645400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1528800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1517700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1582900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1448400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1507000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1523300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1428200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1203600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1192200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1069700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1019000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>910500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1242200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1147100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1065000</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>959400</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1171800</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>1077000</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8010,8 +8187,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8132,8 +8312,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8254,130 +8437,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>6205900</v>
+      </c>
+      <c r="E76" s="3">
         <v>5875300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>6438400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5908400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5977600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5668700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5658500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>6100600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5663400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5281800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5973800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5628000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>6070100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5936700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5247000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5107400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4692100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4745900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4940900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5092500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4956200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4278500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4136200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4212500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4437800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4225600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4480800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4656600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>4681900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>4291200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>4196300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3997200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>4054600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3971900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>4565400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>4465000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>4386200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4257500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>4360000</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>4308300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8498,257 +8687,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>423900</v>
+      </c>
+      <c r="E81" s="3">
         <v>288900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>294800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>304600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>327300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>345600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>299900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>321000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>343300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>303800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>439800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>291100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>413800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>335700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>374300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>370100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>457400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>329700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>332100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>232100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>204600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>182000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>140200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>102400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>138500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>162900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>186900</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>207000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>265100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>132000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>205100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>158900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>208100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>182600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>209300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>196800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>234900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>205800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>187300</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>218500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8791,121 +8989,122 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3800</v>
+      </c>
+      <c r="E83" s="3">
         <v>14300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>14100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>16600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>6400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>15200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>17700</v>
       </c>
-      <c r="J83" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="K83" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L83" s="3">
         <v>12300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>20300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>18200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>16800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>11900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>19200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>23100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>23800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>22400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>22500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>23200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>24200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>24100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>20900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>7400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>35500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>21900</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>22000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>23700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>23400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>24100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>22400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>12400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>11700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>11900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>11700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>13300</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>13200</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>12700</v>
-      </c>
-      <c r="AN83" s="3">
-        <v>12600</v>
       </c>
       <c r="AO83" s="3">
         <v>12600</v>
@@ -8913,8 +9112,11 @@
       <c r="AP83" s="3">
         <v>12600</v>
       </c>
+      <c r="AQ83" s="3">
+        <v>12600</v>
+      </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9035,8 +9237,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9157,8 +9362,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9279,8 +9487,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9401,8 +9612,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9523,130 +9737,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>176900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1983500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1910900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-1467800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1358200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-343000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>502400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>739600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-200300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-589500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1563000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2324000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-54900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1070200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1185300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>43000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-119400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1534500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>822300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>3030800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>2196700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-2712800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>767600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>305800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-843300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>291100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>1097500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>66100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-970600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>1334400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-614600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-434900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-266200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>136000</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>703800</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>250800</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>435500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>179000</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>398600</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-193700</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9689,130 +9909,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-5900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-4300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-10100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-33219000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-18302000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-17061000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-9558000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-16086000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-16424000</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-400</v>
       </c>
       <c r="X91" s="3">
         <v>-400</v>
       </c>
       <c r="Y91" s="3">
+        <v>-400</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-300</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
-      </c>
       <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-16900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-15800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-23800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-8600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-12800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-10800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-3200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-10300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-10500</v>
-      </c>
-      <c r="AM91" s="3">
-        <v>-6700</v>
       </c>
       <c r="AN91" s="3">
         <v>-6700</v>
       </c>
       <c r="AO91" s="3">
+        <v>-6700</v>
+      </c>
+      <c r="AP91" s="3">
         <v>-12200</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-10700</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9933,8 +10157,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10055,130 +10282,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-16400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-27400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-14200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-18100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-14800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-20300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-24100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-25300</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-21100</v>
       </c>
       <c r="P94" s="3">
         <v>-21100</v>
       </c>
       <c r="Q94" s="3">
+        <v>-21100</v>
+      </c>
+      <c r="R94" s="3">
         <v>-32300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-19800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-16000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-73500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-1665400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-1869400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-36000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>177700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>379100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>37600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-365700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-81200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-143800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>82600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-374100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>365300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>88000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-36700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>110800</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-319300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-565800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-682600</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-165900</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>8300</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>260000</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10221,17 +10454,18 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>0</v>
+      </c>
+      <c r="E96" s="3">
         <v>1086200</v>
       </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
       <c r="F96" s="3">
         <v>0</v>
       </c>
@@ -10239,11 +10473,11 @@
         <v>0</v>
       </c>
       <c r="H96" s="3">
+        <v>0</v>
+      </c>
+      <c r="I96" s="3">
         <v>1045800</v>
       </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
       <c r="J96" s="3">
         <v>0</v>
       </c>
@@ -10251,11 +10485,11 @@
         <v>0</v>
       </c>
       <c r="L96" s="3">
+        <v>0</v>
+      </c>
+      <c r="M96" s="3">
         <v>832800</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
-      </c>
       <c r="N96" s="3">
         <v>0</v>
       </c>
@@ -10263,11 +10497,11 @@
         <v>0</v>
       </c>
       <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3">
         <v>1094400</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
-      </c>
       <c r="R96" s="3">
         <v>0</v>
       </c>
@@ -10275,11 +10509,11 @@
         <v>0</v>
       </c>
       <c r="T96" s="3">
+        <v>0</v>
+      </c>
+      <c r="U96" s="3">
         <v>-610000</v>
       </c>
-      <c r="U96" s="3">
-        <v>0</v>
-      </c>
       <c r="V96" s="3">
         <v>0</v>
       </c>
@@ -10287,11 +10521,11 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-246700</v>
       </c>
-      <c r="Y96" s="3">
-        <v>0</v>
-      </c>
       <c r="Z96" s="3">
         <v>0</v>
       </c>
@@ -10299,11 +10533,11 @@
         <v>0</v>
       </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-417100</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
         <v>0</v>
       </c>
@@ -10311,11 +10545,11 @@
         <v>0</v>
       </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-463200</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
         <v>0</v>
       </c>
@@ -10323,11 +10557,11 @@
         <v>0</v>
       </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-478800</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
       <c r="AL96" s="3">
         <v>0</v>
       </c>
@@ -10335,16 +10569,19 @@
         <v>0</v>
       </c>
       <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-502800</v>
       </c>
-      <c r="AO96" s="3">
-        <v>0</v>
-      </c>
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10465,8 +10702,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10587,8 +10827,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10709,370 +10952,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-605100</v>
+      </c>
+      <c r="E100" s="3">
         <v>727000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1645600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1066000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-686500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>865000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>133400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1185400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-361900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-291100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>421600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-290100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>24500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-559300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>572700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-392400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-335500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-756000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>643800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-436700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1230300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>185600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-188600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-941600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>3176000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-140500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-231800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1168000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>919100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-701800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>575400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>283400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>152300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-199200</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>237400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-152300</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>17700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>92300</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-55300</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>329700</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-30300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-39800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>125700</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-81200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-77600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>189600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-27400</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="K101" s="3">
+      <c r="K101" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L101" s="3">
         <v>22600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-151700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-243600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>126800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>363000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-274300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-223500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>132700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>359500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-244000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>115000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>197000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>70600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>16100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-98500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-69700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>99400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>40800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-14300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>56700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-6700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>11300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>34800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>36400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>86400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-10300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-34600</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-12900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>10300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-19200</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>14300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-12600</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-456700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1204700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>174700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-369300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>630200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>465800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>753200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-545000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-654500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-711300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1193000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2167300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-28900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1802300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1502300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-236100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-111700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-2545200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1507600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1125800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1628100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2547200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>682100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-351400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>2469700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-174300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>770200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1147000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>26200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>268000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>360800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-27200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-64200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>37300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>587400</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-480200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-219200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>86200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>365900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>383400</v>
       </c>
     </row>
